--- a/internal_ratings_2024.xlsx
+++ b/internal_ratings_2024.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>Code</t>
   </si>
@@ -43,6 +43,9 @@
     <t>CHL</t>
   </si>
   <si>
+    <t>CHN</t>
+  </si>
+  <si>
     <t>COL</t>
   </si>
   <si>
@@ -88,6 +91,9 @@
     <t>ITA</t>
   </si>
   <si>
+    <t>JPN</t>
+  </si>
+  <si>
     <t>KOR</t>
   </si>
   <si>
@@ -125,6 +131,9 @@
   </si>
   <si>
     <t>USA</t>
+  </si>
+  <si>
+    <t>VNM</t>
   </si>
   <si>
     <t>ZAF</t>
@@ -485,7 +494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -510,7 +519,7 @@
         <v>2024</v>
       </c>
       <c r="C2">
-        <v>2.088266658985214</v>
+        <v>2.225865252514395</v>
       </c>
       <c r="D2">
         <v>2</v>
@@ -524,7 +533,7 @@
         <v>2024</v>
       </c>
       <c r="C3">
-        <v>13.35074448556182</v>
+        <v>13.3241624337704</v>
       </c>
       <c r="D3">
         <v>13</v>
@@ -538,7 +547,7 @@
         <v>2024</v>
       </c>
       <c r="C4">
-        <v>9.865700379617621</v>
+        <v>9.833130006637976</v>
       </c>
       <c r="D4">
         <v>10</v>
@@ -552,7 +561,7 @@
         <v>2024</v>
       </c>
       <c r="C5">
-        <v>20.27773385361852</v>
+        <v>20.30594534348597</v>
       </c>
       <c r="D5">
         <v>21</v>
@@ -566,7 +575,7 @@
         <v>2024</v>
       </c>
       <c r="C6">
-        <v>14.94059516628488</v>
+        <v>14.96337843032584</v>
       </c>
       <c r="D6">
         <v>15</v>
@@ -580,10 +589,10 @@
         <v>2024</v>
       </c>
       <c r="C7">
-        <v>11.65875264188075</v>
+        <v>16.53448224361307</v>
       </c>
       <c r="D7">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -594,10 +603,10 @@
         <v>2024</v>
       </c>
       <c r="C8">
-        <v>17.95650617164695</v>
+        <v>11.6130674407008</v>
       </c>
       <c r="D8">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -608,10 +617,10 @@
         <v>2024</v>
       </c>
       <c r="C9">
-        <v>20.90597652139212</v>
+        <v>17.96805486175688</v>
       </c>
       <c r="D9">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -622,10 +631,10 @@
         <v>2024</v>
       </c>
       <c r="C10">
-        <v>4.619729521644081</v>
+        <v>20.87037509096333</v>
       </c>
       <c r="D10">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -636,10 +645,10 @@
         <v>2024</v>
       </c>
       <c r="C11">
-        <v>5.610617474353824</v>
+        <v>4.668743364530286</v>
       </c>
       <c r="D11">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -650,10 +659,10 @@
         <v>2024</v>
       </c>
       <c r="C12">
-        <v>15.0443691701614</v>
+        <v>5.601177822865219</v>
       </c>
       <c r="D12">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -664,10 +673,10 @@
         <v>2024</v>
       </c>
       <c r="C13">
-        <v>17.82112310912314</v>
+        <v>15.03549602134817</v>
       </c>
       <c r="D13">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -678,7 +687,7 @@
         <v>2024</v>
       </c>
       <c r="C14">
-        <v>17.80556943855542</v>
+        <v>17.85175721767591</v>
       </c>
       <c r="D14">
         <v>18</v>
@@ -692,10 +701,10 @@
         <v>2024</v>
       </c>
       <c r="C15">
-        <v>11.73845435651521</v>
+        <v>17.85831597000088</v>
       </c>
       <c r="D15">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -706,10 +715,10 @@
         <v>2024</v>
       </c>
       <c r="C16">
-        <v>12.88584626007935</v>
+        <v>11.68394949851366</v>
       </c>
       <c r="D16">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -720,7 +729,7 @@
         <v>2024</v>
       </c>
       <c r="C17">
-        <v>13.00425547133698</v>
+        <v>12.86394831811178</v>
       </c>
       <c r="D17">
         <v>13</v>
@@ -734,10 +743,10 @@
         <v>2024</v>
       </c>
       <c r="C18">
-        <v>11.87258228493775</v>
+        <v>12.979880819654</v>
       </c>
       <c r="D18">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -748,10 +757,10 @@
         <v>2024</v>
       </c>
       <c r="C19">
-        <v>18.81740487236837</v>
+        <v>11.83938466982375</v>
       </c>
       <c r="D19">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -762,10 +771,10 @@
         <v>2024</v>
       </c>
       <c r="C20">
-        <v>16.21312702959958</v>
+        <v>18.94361234256269</v>
       </c>
       <c r="D20">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -776,10 +785,10 @@
         <v>2024</v>
       </c>
       <c r="C21">
-        <v>12.83948913847312</v>
+        <v>16.28230841959284</v>
       </c>
       <c r="D21">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -790,10 +799,10 @@
         <v>2024</v>
       </c>
       <c r="C22">
-        <v>18.02420427683595</v>
+        <v>12.8248466889546</v>
       </c>
       <c r="D22">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -804,10 +813,10 @@
         <v>2024</v>
       </c>
       <c r="C23">
-        <v>11.86868665608419</v>
+        <v>16.294736466178</v>
       </c>
       <c r="D23">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -818,10 +827,10 @@
         <v>2024</v>
       </c>
       <c r="C24">
-        <v>14.23110474656785</v>
+        <v>18.04535430104481</v>
       </c>
       <c r="D24">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -832,10 +841,10 @@
         <v>2024</v>
       </c>
       <c r="C25">
-        <v>13.2610121848978</v>
+        <v>11.81461252194676</v>
       </c>
       <c r="D25">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -846,10 +855,10 @@
         <v>2024</v>
       </c>
       <c r="C26">
-        <v>12.86270671093465</v>
+        <v>14.21798064603747</v>
       </c>
       <c r="D26">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -860,10 +869,10 @@
         <v>2024</v>
       </c>
       <c r="C27">
-        <v>14.76585986121692</v>
+        <v>13.21507387391303</v>
       </c>
       <c r="D27">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -874,10 +883,10 @@
         <v>2024</v>
       </c>
       <c r="C28">
-        <v>14.49970195632286</v>
+        <v>12.8502312346076</v>
       </c>
       <c r="D28">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -888,10 +897,10 @@
         <v>2024</v>
       </c>
       <c r="C29">
-        <v>11.87699449518986</v>
+        <v>14.77360813400583</v>
       </c>
       <c r="D29">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -902,10 +911,10 @@
         <v>2024</v>
       </c>
       <c r="C30">
-        <v>20.93555616583582</v>
+        <v>14.47566403167482</v>
       </c>
       <c r="D30">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -916,10 +925,10 @@
         <v>2024</v>
       </c>
       <c r="C31">
-        <v>13.98834063232031</v>
+        <v>11.88589528781065</v>
       </c>
       <c r="D31">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -930,10 +939,10 @@
         <v>2024</v>
       </c>
       <c r="C32">
-        <v>6.842320859350338</v>
+        <v>20.9093656276427</v>
       </c>
       <c r="D32">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -944,7 +953,7 @@
         <v>2024</v>
       </c>
       <c r="C33">
-        <v>13.51358633632353</v>
+        <v>13.94078900390956</v>
       </c>
       <c r="D33">
         <v>14</v>
@@ -958,10 +967,10 @@
         <v>2024</v>
       </c>
       <c r="C34">
-        <v>20.52068461743615</v>
+        <v>6.787778524911686</v>
       </c>
       <c r="D34">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -972,9 +981,51 @@
         <v>2024</v>
       </c>
       <c r="C35">
-        <v>8.969127320559844</v>
+        <v>13.5558576601462</v>
       </c>
       <c r="D35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36">
+        <v>2024</v>
+      </c>
+      <c r="C36">
+        <v>20.53531715623857</v>
+      </c>
+      <c r="D36">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37">
+        <v>2024</v>
+      </c>
+      <c r="C37">
+        <v>10.96155012663614</v>
+      </c>
+      <c r="D37">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38">
+        <v>2024</v>
+      </c>
+      <c r="C38">
+        <v>8.902904682610011</v>
+      </c>
+      <c r="D38">
         <v>9</v>
       </c>
     </row>

--- a/internal_ratings_2024.xlsx
+++ b/internal_ratings_2024.xlsx
@@ -519,7 +519,7 @@
         <v>2024</v>
       </c>
       <c r="C2">
-        <v>2.225865252514395</v>
+        <v>2.225863991480994</v>
       </c>
       <c r="D2">
         <v>2</v>
@@ -533,7 +533,7 @@
         <v>2024</v>
       </c>
       <c r="C3">
-        <v>13.3241624337704</v>
+        <v>13.32416111645554</v>
       </c>
       <c r="D3">
         <v>13</v>
@@ -547,7 +547,7 @@
         <v>2024</v>
       </c>
       <c r="C4">
-        <v>9.833130006637976</v>
+        <v>9.833128613378863</v>
       </c>
       <c r="D4">
         <v>10</v>
@@ -561,7 +561,7 @@
         <v>2024</v>
       </c>
       <c r="C5">
-        <v>20.30594534348597</v>
+        <v>20.30594407844117</v>
       </c>
       <c r="D5">
         <v>21</v>
@@ -575,7 +575,7 @@
         <v>2024</v>
       </c>
       <c r="C6">
-        <v>14.96337843032584</v>
+        <v>14.96337729974069</v>
       </c>
       <c r="D6">
         <v>15</v>
@@ -589,7 +589,7 @@
         <v>2024</v>
       </c>
       <c r="C7">
-        <v>16.53448224361307</v>
+        <v>16.53448092797379</v>
       </c>
       <c r="D7">
         <v>17</v>
@@ -603,7 +603,7 @@
         <v>2024</v>
       </c>
       <c r="C8">
-        <v>11.6130674407008</v>
+        <v>11.61306627208324</v>
       </c>
       <c r="D8">
         <v>12</v>
@@ -617,7 +617,7 @@
         <v>2024</v>
       </c>
       <c r="C9">
-        <v>17.96805486175688</v>
+        <v>17.96805347906439</v>
       </c>
       <c r="D9">
         <v>18</v>
@@ -631,7 +631,7 @@
         <v>2024</v>
       </c>
       <c r="C10">
-        <v>20.87037509096333</v>
+        <v>20.87037471970534</v>
       </c>
       <c r="D10">
         <v>21</v>
@@ -645,7 +645,7 @@
         <v>2024</v>
       </c>
       <c r="C11">
-        <v>4.668743364530286</v>
+        <v>4.668742110419251</v>
       </c>
       <c r="D11">
         <v>4</v>
@@ -659,7 +659,7 @@
         <v>2024</v>
       </c>
       <c r="C12">
-        <v>5.601177822865219</v>
+        <v>5.601176086923541</v>
       </c>
       <c r="D12">
         <v>6</v>
@@ -673,7 +673,7 @@
         <v>2024</v>
       </c>
       <c r="C13">
-        <v>15.03549602134817</v>
+        <v>15.03549486317858</v>
       </c>
       <c r="D13">
         <v>15</v>
@@ -687,7 +687,7 @@
         <v>2024</v>
       </c>
       <c r="C14">
-        <v>17.85175721767591</v>
+        <v>17.85175588827137</v>
       </c>
       <c r="D14">
         <v>18</v>
@@ -701,7 +701,7 @@
         <v>2024</v>
       </c>
       <c r="C15">
-        <v>17.85831597000088</v>
+        <v>17.85831464800933</v>
       </c>
       <c r="D15">
         <v>18</v>
@@ -715,7 +715,7 @@
         <v>2024</v>
       </c>
       <c r="C16">
-        <v>11.68394949851366</v>
+        <v>11.68394845303637</v>
       </c>
       <c r="D16">
         <v>12</v>
@@ -729,7 +729,7 @@
         <v>2024</v>
       </c>
       <c r="C17">
-        <v>12.86394831811178</v>
+        <v>12.86394707043234</v>
       </c>
       <c r="D17">
         <v>13</v>
@@ -743,7 +743,7 @@
         <v>2024</v>
       </c>
       <c r="C18">
-        <v>12.979880819654</v>
+        <v>12.97987956060451</v>
       </c>
       <c r="D18">
         <v>13</v>
@@ -757,7 +757,7 @@
         <v>2024</v>
       </c>
       <c r="C19">
-        <v>11.83938466982375</v>
+        <v>11.83938370312738</v>
       </c>
       <c r="D19">
         <v>12</v>
@@ -771,7 +771,7 @@
         <v>2024</v>
       </c>
       <c r="C20">
-        <v>18.94361234256269</v>
+        <v>18.94361068321217</v>
       </c>
       <c r="D20">
         <v>19</v>
@@ -785,7 +785,7 @@
         <v>2024</v>
       </c>
       <c r="C21">
-        <v>16.28230841959284</v>
+        <v>16.28230702551454</v>
       </c>
       <c r="D21">
         <v>16</v>
@@ -799,7 +799,7 @@
         <v>2024</v>
       </c>
       <c r="C22">
-        <v>12.8248466889546</v>
+        <v>12.82484545424393</v>
       </c>
       <c r="D22">
         <v>13</v>
@@ -813,7 +813,7 @@
         <v>2024</v>
       </c>
       <c r="C23">
-        <v>16.294736466178</v>
+        <v>16.29473507553952</v>
       </c>
       <c r="D23">
         <v>16</v>
@@ -827,7 +827,7 @@
         <v>2024</v>
       </c>
       <c r="C24">
-        <v>18.04535430104481</v>
+        <v>18.04535290755415</v>
       </c>
       <c r="D24">
         <v>18</v>
@@ -841,7 +841,7 @@
         <v>2024</v>
       </c>
       <c r="C25">
-        <v>11.81461252194676</v>
+        <v>11.81461147097419</v>
       </c>
       <c r="D25">
         <v>12</v>
@@ -855,7 +855,7 @@
         <v>2024</v>
       </c>
       <c r="C26">
-        <v>14.21798064603747</v>
+        <v>14.21797947675288</v>
       </c>
       <c r="D26">
         <v>14</v>
@@ -869,7 +869,7 @@
         <v>2024</v>
       </c>
       <c r="C27">
-        <v>13.21507387391303</v>
+        <v>13.21507257683247</v>
       </c>
       <c r="D27">
         <v>13</v>
@@ -883,7 +883,7 @@
         <v>2024</v>
       </c>
       <c r="C28">
-        <v>12.8502312346076</v>
+        <v>12.85022999927303</v>
       </c>
       <c r="D28">
         <v>13</v>
@@ -897,7 +897,7 @@
         <v>2024</v>
       </c>
       <c r="C29">
-        <v>14.77360813400583</v>
+        <v>14.77360699994524</v>
       </c>
       <c r="D29">
         <v>15</v>
@@ -911,7 +911,7 @@
         <v>2024</v>
       </c>
       <c r="C30">
-        <v>14.47566403167482</v>
+        <v>14.47566278236686</v>
       </c>
       <c r="D30">
         <v>15</v>
@@ -925,7 +925,7 @@
         <v>2024</v>
       </c>
       <c r="C31">
-        <v>11.88589528781065</v>
+        <v>11.88589430460035</v>
       </c>
       <c r="D31">
         <v>12</v>
@@ -939,7 +939,7 @@
         <v>2024</v>
       </c>
       <c r="C32">
-        <v>20.9093656276427</v>
+        <v>20.9093653629342</v>
       </c>
       <c r="D32">
         <v>21</v>
@@ -953,7 +953,7 @@
         <v>2024</v>
       </c>
       <c r="C33">
-        <v>13.94078900390956</v>
+        <v>13.94078775387767</v>
       </c>
       <c r="D33">
         <v>14</v>
@@ -967,7 +967,7 @@
         <v>2024</v>
       </c>
       <c r="C34">
-        <v>6.787778524911686</v>
+        <v>6.787776543922241</v>
       </c>
       <c r="D34">
         <v>7</v>
@@ -981,7 +981,7 @@
         <v>2024</v>
       </c>
       <c r="C35">
-        <v>13.5558576601462</v>
+        <v>13.5558564382852</v>
       </c>
       <c r="D35">
         <v>14</v>
@@ -995,7 +995,7 @@
         <v>2024</v>
       </c>
       <c r="C36">
-        <v>20.53531715623857</v>
+        <v>20.53531615621721</v>
       </c>
       <c r="D36">
         <v>21</v>
@@ -1009,7 +1009,7 @@
         <v>2024</v>
       </c>
       <c r="C37">
-        <v>10.96155012663614</v>
+        <v>10.96154861439421</v>
       </c>
       <c r="D37">
         <v>11</v>
@@ -1023,7 +1023,7 @@
         <v>2024</v>
       </c>
       <c r="C38">
-        <v>8.902904682610011</v>
+        <v>8.902903445363137</v>
       </c>
       <c r="D38">
         <v>9</v>
